--- a/Proiect/Proiect/Output/Rapoarte/Rezultate_VIF.xlsx
+++ b/Proiect/Proiect/Output/Rapoarte/Rezultate_VIF.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -373,7 +373,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>1.689099400723527</v>
+        <v>2.499685668541002</v>
       </c>
     </row>
     <row r="3">
@@ -383,7 +383,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>11.52675879389651</v>
+        <v>1.952952007611464</v>
       </c>
     </row>
     <row r="4">
@@ -393,37 +393,27 @@
         </is>
       </c>
       <c r="B4">
-        <v>4.084807633743103</v>
+        <v>1.616295717422371</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ln_Politie</t>
+          <t>ln_Densitate</t>
         </is>
       </c>
       <c r="B5">
-        <v>13.53722465834104</v>
+        <v>1.194502779273453</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ln_Densitate</t>
+          <t>Est_Vest</t>
         </is>
       </c>
       <c r="B6">
-        <v>1.891989588142346</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Membru_UE</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>1.538679643155966</v>
+        <v>2.692983574246222</v>
       </c>
     </row>
   </sheetData>
